--- a/artfynd/A 19284-2022 artfynd.xlsx
+++ b/artfynd/A 19284-2022 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115196537</v>
+        <v>115196536</v>
       </c>
       <c r="B2" t="n">
-        <v>95923</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>293676</v>
+        <v>293653</v>
       </c>
       <c r="R2" t="n">
-        <v>6495514</v>
+        <v>6495543</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115196555</v>
+        <v>115196537</v>
       </c>
       <c r="B3" t="n">
-        <v>96283</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2606</v>
+        <v>2569</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>293638</v>
+        <v>293676</v>
       </c>
       <c r="R3" t="n">
-        <v>6495556</v>
+        <v>6495514</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115196536</v>
+        <v>115196538</v>
       </c>
       <c r="B4" t="n">
-        <v>95923</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>293653</v>
+        <v>293636</v>
       </c>
       <c r="R4" t="n">
-        <v>6495543</v>
+        <v>6495546</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>115196540</v>
+        <v>115196539</v>
       </c>
       <c r="B5" t="n">
-        <v>95923</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1021,7 +1001,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>293625</v>
+        <v>293622</v>
       </c>
       <c r="R5" t="n">
         <v>6495520</v>
@@ -1083,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>115196542</v>
+        <v>115196540</v>
       </c>
       <c r="B6" t="n">
-        <v>95923</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1123,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>293610</v>
+        <v>293625</v>
       </c>
       <c r="R6" t="n">
-        <v>6495503</v>
+        <v>6495520</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>115196530</v>
+        <v>115196541</v>
       </c>
       <c r="B7" t="n">
-        <v>94069</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2810</v>
+        <v>2569</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>293609</v>
+        <v>293615</v>
       </c>
       <c r="R7" t="n">
-        <v>6495505</v>
+        <v>6495512</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>115196543</v>
+        <v>115196542</v>
       </c>
       <c r="B8" t="n">
-        <v>95923</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1327,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>293611</v>
+        <v>293610</v>
       </c>
       <c r="R8" t="n">
-        <v>6495491</v>
+        <v>6495503</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,15 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>115196538</v>
+        <v>115196543</v>
       </c>
       <c r="B9" t="n">
-        <v>95923</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1429,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>293636</v>
+        <v>293611</v>
       </c>
       <c r="R9" t="n">
-        <v>6495546</v>
+        <v>6495491</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,15 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>115196529</v>
+        <v>115196548</v>
       </c>
       <c r="B10" t="n">
-        <v>94069</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1507,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2810</v>
+        <v>2569</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>293619</v>
+        <v>293692</v>
       </c>
       <c r="R10" t="n">
-        <v>6495524</v>
+        <v>6495552</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,15 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>115196541</v>
+        <v>115196555</v>
       </c>
       <c r="B11" t="n">
-        <v>95923</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97785</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1609,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2569</v>
+        <v>2606</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>293615</v>
+        <v>293638</v>
       </c>
       <c r="R11" t="n">
-        <v>6495512</v>
+        <v>6495556</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,15 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>115196558</v>
+        <v>115196529</v>
       </c>
       <c r="B12" t="n">
-        <v>74585</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1711,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6426</v>
+        <v>2810</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>293599</v>
+        <v>293619</v>
       </c>
       <c r="R12" t="n">
-        <v>6495490</v>
+        <v>6495524</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,15 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>115196539</v>
+        <v>115196530</v>
       </c>
       <c r="B13" t="n">
-        <v>95923</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1813,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2569</v>
+        <v>2810</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>293622</v>
+        <v>293609</v>
       </c>
       <c r="R13" t="n">
-        <v>6495520</v>
+        <v>6495505</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,37 +1839,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>115196548</v>
+        <v>115196558</v>
       </c>
       <c r="B14" t="n">
-        <v>95923</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2569</v>
+        <v>6426</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>293692</v>
+        <v>293599</v>
       </c>
       <c r="R14" t="n">
-        <v>6495552</v>
+        <v>6495490</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 19284-2022 artfynd.xlsx
+++ b/artfynd/A 19284-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115196536</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115196537</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115196538</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115196539</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115196540</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115196541</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115196542</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115196543</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115196548</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115196555</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115196529</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115196530</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,8 +1998,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115196558</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>